--- a/output/pdf_financials_xlsx/TRU.xlsx
+++ b/output/pdf_financials_xlsx/TRU.xlsx
@@ -1074,13 +1074,13 @@
         <v>-0.103152</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>8.116237</v>
+        <v>-8.116237</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>4.218424</v>
+        <v>-4.218424</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>2.143175</v>
+        <v>-2.143175</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>1.132594</v>
@@ -1296,13 +1296,13 @@
         <v>-0.041676</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>8.116237</v>
+        <v>-8.116237</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>4.218424</v>
+        <v>-4.218424</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2.143175</v>
+        <v>-2.143175</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>1.132594</v>
@@ -1427,13 +1427,13 @@
         <v>-0.041676</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>8.116237</v>
+        <v>-8.116237</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>4.218424</v>
+        <v>-4.218424</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>2.143175</v>
+        <v>-2.143175</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>1.132594</v>
@@ -1588,13 +1588,13 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-50.726481</v>
+        <v>50.726481</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-70.307067</v>
+        <v>70.307067</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-107.15875</v>
+        <v>107.15875</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
@@ -1637,13 +1637,13 @@
         <v>-0.103152</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>8.116237</v>
+        <v>-8.116237</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>4.218424</v>
+        <v>-4.218424</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>2.143175</v>
+        <v>-2.143175</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>1.132594</v>
@@ -1725,13 +1725,13 @@
         <v>-0.103152</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>8.116237</v>
+        <v>-8.116237</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>4.218424</v>
+        <v>-4.218424</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>2.143175</v>
+        <v>-2.143175</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>1.132594</v>
@@ -1825,13 +1825,13 @@
         <v>-59.5974872033504</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>0</v>
@@ -4477,40 +4477,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.052035</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.193472</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.662889</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.572334</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.471789</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.122731</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.122731</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.7364</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>4.564507</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>5.545564</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>5.577179</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>5.577179</v>
       </c>
     </row>
     <row r="93">
@@ -7138,7 +7138,11 @@
           <t>Share-based payment reserves (Notes 7 and 8)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -7658,7 +7662,11 @@
           <t>Share-based payment reserves (Notes 8 and 9)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -8118,7 +8126,11 @@
           <t>Share-based payment reserves (Notes 10 and 11)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -9122,7 +9134,11 @@
           <t>Share-based payment reserves (Notes 11 and 12)</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -9926,7 +9942,11 @@
           <t>RESERVES</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -15808,7 +15828,11 @@
           <t>RESERVES 16</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E125" s="5" t="n">
         <v>0.052035</v>
       </c>
@@ -25897,16 +25921,16 @@
         </is>
       </c>
       <c r="L261" s="5" t="n">
-        <v>8.116237</v>
+        <v>-8.116237</v>
       </c>
       <c r="M261" s="5" t="n">
-        <v>4.218424</v>
+        <v>-4.218424</v>
       </c>
       <c r="N261" s="5" t="n">
-        <v>2.143175</v>
+        <v>-2.143175</v>
       </c>
       <c r="O261" s="5" t="n">
-        <v>1.132594</v>
+        <v>-1.132594</v>
       </c>
       <c r="P261" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/TRU.xlsx
+++ b/output/pdf_financials_xlsx/TRU.xlsx
@@ -879,40 +879,40 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.10729</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.032889</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.005198</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.034147</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.010107</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.013302</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.027762</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.018847</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.017687</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.058846</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.091117</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.052793</v>
       </c>
     </row>
     <row r="13">
@@ -1614,16 +1614,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1.224584</v>
+        <v>1.117294</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.951096</v>
+        <v>1.918207</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.219573</v>
+        <v>1.214375</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3.02512</v>
+        <v>2.990973</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -1631,25 +1631,25 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.612231</v>
+        <v>-0.625533</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.103152</v>
+        <v>-0.130914</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-8.116237</v>
+        <v>-8.097390000000001</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-4.218424</v>
+        <v>-4.200737</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.143175</v>
+        <v>-2.084329</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1.132594</v>
+        <v>1.223711</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.010252</v>
+        <v>0.042541</v>
       </c>
     </row>
     <row r="28">
@@ -1702,16 +1702,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1.224584</v>
+        <v>1.117294</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.951096</v>
+        <v>1.918207</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.219573</v>
+        <v>1.214375</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.02512</v>
+        <v>2.990973</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -1719,25 +1719,25 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.612231</v>
+        <v>-0.625533</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.103152</v>
+        <v>-0.130914</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-8.116237</v>
+        <v>-8.097390000000001</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-4.218424</v>
+        <v>-4.200737</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.143175</v>
+        <v>-2.084329</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.132594</v>
+        <v>1.223711</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.010252</v>
+        <v>0.042541</v>
       </c>
     </row>
     <row r="30">
@@ -1747,16 +1747,16 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>29.1793202983354</v>
+        <v>26.62282007065939</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>45.76114560944468</v>
+        <v>44.98976464308063</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>149.6195633504925</v>
+        <v>148.981862704204</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>2235.216752007921</v>
+        <v>2209.986035067497</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-4342.679812739396</v>
+        <v>-4437.033621790325</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-37.13682937190833</v>
+        <v>-47.13171708153023</v>
       </c>
       <c r="I30" s="1" t="inlineStr">
         <is>
@@ -5842,10 +5842,10 @@
         <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0108</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0396</v>
       </c>
       <c r="K124" s="3" t="n">
         <v>0</v>
@@ -5885,10 +5885,10 @@
         <v>0</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0108</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0396</v>
       </c>
       <c r="K125" s="3" t="n">
         <v>0</v>
@@ -18744,7 +18744,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -23862,7 +23866,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -31376,7 +31380,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -37184,7 +37188,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -38396,7 +38400,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E428" s="5" t="n">

--- a/output/pdf_financials_xlsx/TRU.xlsx
+++ b/output/pdf_financials_xlsx/TRU.xlsx
@@ -1680,10 +1680,10 @@
         <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.010641</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.039016</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0</v>
@@ -1725,10 +1725,10 @@
         <v>-0.130914</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-8.097390000000001</v>
+        <v>-8.086748999999999</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-4.200737</v>
+        <v>-4.161721</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-2.084329</v>
@@ -4808,10 +4808,10 @@
         <v>0</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.010641</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.039016</v>
       </c>
       <c r="K100" s="3" t="n">
         <v>0</v>
@@ -18222,7 +18222,11 @@
           <t>Depreciation on right-of-use asset</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TRU.xlsx
+++ b/output/pdf_financials_xlsx/TRU.xlsx
@@ -1282,15 +1282,13 @@
         <v>0.325465</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.061694</v>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.004949</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>-0.353384</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-0.114167</v>
+        <v>-0.524264</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-0.041676</v>
@@ -4777,7 +4775,7 @@
         <v>-1.132594</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>-0.010252</v>
+        <v>0.010252</v>
       </c>
     </row>
     <row r="100">
@@ -5260,16 +5258,16 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.207907</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.472138</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.490733</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002115</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -5392,13 +5390,13 @@
         <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>-0.461156</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0</v>
+        <v>-0.011681</v>
       </c>
       <c r="F114" s="3" t="n">
         <v>0</v>
@@ -6277,16 +6275,16 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.207907</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.472138</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.490733</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002115</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -6320,16 +6318,16 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>0.954469</v>
+        <v>0.7465619999999999</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>0.729973</v>
+        <v>0.257835</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>0.157071</v>
+        <v>-0.333662</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.47545</v>
+        <v>-0.477565</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-0.646361</v>
@@ -15906,7 +15904,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -21730,7 +21732,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -21872,7 +21878,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E207" s="5" t="n">
         <v>-0.207907</v>
       </c>
@@ -32690,7 +32700,11 @@
           <t>LOSS FROM CONTINUING OPERATIONS</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E352" t="inlineStr">
         <is>
           <t>-</t>
@@ -33978,7 +33992,11 @@
           <t>LOSS FROM CONTINUING OPERATIONS</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E369" t="inlineStr">
         <is>
           <t>-</t>
@@ -34806,7 +34824,11 @@
           <t>LOSS FROM CONTINUING OPERATIONS</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
           <t>-</t>
